--- a/data/exports/predictions/daily_lotto_predictions.xlsx
+++ b/data/exports/predictions/daily_lotto_predictions.xlsx
@@ -503,22 +503,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C2" t="n">
         <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E2" t="n">
         <v>25</v>
       </c>
       <c r="F2" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="G2" t="n">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H2" t="n">
         <v>2</v>
@@ -527,16 +527,16 @@
         <v>3</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>3491.5541</v>
+        <v>3498.6325</v>
       </c>
       <c r="N2" t="n">
         <v>95</v>
@@ -548,7 +548,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-05-23 08:16:12</t>
+          <t>2026-05-24 05:27:59</t>
         </is>
       </c>
     </row>
@@ -557,22 +557,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" t="n">
         <v>10</v>
       </c>
-      <c r="C3" t="n">
-        <v>12</v>
-      </c>
       <c r="D3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E3" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F3" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="G3" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
@@ -590,10 +590,10 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3486.8871</v>
+        <v>3491.5966</v>
       </c>
       <c r="N3" t="n">
-        <v>94.95</v>
+        <v>94.93000000000001</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-05-23 08:16:12</t>
+          <t>2026-05-24 05:27:59</t>
         </is>
       </c>
     </row>
@@ -611,22 +611,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E4" t="n">
+        <v>21</v>
+      </c>
+      <c r="F4" t="n">
         <v>25</v>
       </c>
-      <c r="F4" t="n">
-        <v>35</v>
-      </c>
       <c r="G4" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H4" t="n">
         <v>2</v>
@@ -644,10 +644,10 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3481.7205</v>
+        <v>3486.942</v>
       </c>
       <c r="N4" t="n">
-        <v>94.90000000000001</v>
+        <v>94.88</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -656,7 +656,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-05-23 08:16:12</t>
+          <t>2026-05-24 05:27:59</t>
         </is>
       </c>
     </row>
@@ -677,10 +677,10 @@
         <v>25</v>
       </c>
       <c r="F5" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="G5" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="H5" t="n">
         <v>2</v>
@@ -698,10 +698,10 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3481.7145</v>
+        <v>3484.8948</v>
       </c>
       <c r="N5" t="n">
-        <v>94.90000000000001</v>
+        <v>94.86</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-05-23 08:16:12</t>
+          <t>2026-05-24 05:27:59</t>
         </is>
       </c>
     </row>
@@ -719,22 +719,22 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C6" t="n">
         <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F6" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="G6" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="H6" t="n">
         <v>2</v>
@@ -749,13 +749,13 @@
         <v>2</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3479.0724</v>
+        <v>3481.5906</v>
       </c>
       <c r="N6" t="n">
-        <v>94.87</v>
+        <v>94.83</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-05-23 08:16:12</t>
+          <t>2026-05-24 05:27:59</t>
         </is>
       </c>
     </row>
@@ -773,22 +773,22 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C7" t="n">
+        <v>8</v>
+      </c>
+      <c r="D7" t="n">
         <v>10</v>
       </c>
-      <c r="D7" t="n">
-        <v>14</v>
-      </c>
       <c r="E7" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F7" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G7" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="H7" t="n">
         <v>2</v>
@@ -806,10 +806,10 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3477.7727</v>
+        <v>3481.191</v>
       </c>
       <c r="N7" t="n">
-        <v>94.86</v>
+        <v>94.83</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-05-23 08:16:12</t>
+          <t>2026-05-24 05:27:59</t>
         </is>
       </c>
     </row>
@@ -827,22 +827,22 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C8" t="n">
         <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E8" t="n">
         <v>25</v>
       </c>
       <c r="F8" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G8" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="H8" t="n">
         <v>2</v>
@@ -851,19 +851,19 @@
         <v>3</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>3476.1433</v>
+        <v>3479.293</v>
       </c>
       <c r="N8" t="n">
-        <v>94.84999999999999</v>
+        <v>94.81</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-05-23 08:16:12</t>
+          <t>2026-05-24 05:27:59</t>
         </is>
       </c>
     </row>
@@ -884,19 +884,19 @@
         <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
         <v>25</v>
       </c>
       <c r="F9" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="G9" t="n">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="H9" t="n">
         <v>2</v>
@@ -914,10 +914,10 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3476.0291</v>
+        <v>3478.8735</v>
       </c>
       <c r="N9" t="n">
-        <v>94.84</v>
+        <v>94.8</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-05-23 08:16:12</t>
+          <t>2026-05-24 05:27:59</t>
         </is>
       </c>
     </row>
@@ -935,22 +935,22 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E10" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F10" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="G10" t="n">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="H10" t="n">
         <v>2</v>
@@ -965,13 +965,13 @@
         <v>2</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3474.6325</v>
+        <v>3476.1629</v>
       </c>
       <c r="N10" t="n">
-        <v>94.83</v>
+        <v>94.78</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-05-23 08:16:12</t>
+          <t>2026-05-24 05:27:59</t>
         </is>
       </c>
     </row>
@@ -992,19 +992,19 @@
         <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E11" t="n">
+        <v>23</v>
+      </c>
+      <c r="F11" t="n">
         <v>25</v>
       </c>
-      <c r="F11" t="n">
-        <v>35</v>
-      </c>
       <c r="G11" t="n">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H11" t="n">
         <v>2</v>
@@ -1013,19 +1013,19 @@
         <v>3</v>
       </c>
       <c r="J11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3474.5923</v>
+        <v>3475.3186</v>
       </c>
       <c r="N11" t="n">
-        <v>94.83</v>
+        <v>94.77</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-05-23 08:16:12</t>
+          <t>2026-05-24 05:27:59</t>
         </is>
       </c>
     </row>

--- a/data/exports/predictions/daily_lotto_predictions.xlsx
+++ b/data/exports/predictions/daily_lotto_predictions.xlsx
@@ -503,7 +503,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2" t="n">
         <v>10</v>
@@ -515,10 +515,10 @@
         <v>25</v>
       </c>
       <c r="F2" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G2" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="H2" t="n">
         <v>2</v>
@@ -527,16 +527,16 @@
         <v>3</v>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>3498.6325</v>
+        <v>3490.398</v>
       </c>
       <c r="N2" t="n">
         <v>95</v>
@@ -548,7 +548,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-05-24 05:27:59</t>
+          <t>2026-05-25 14:24:55</t>
         </is>
       </c>
     </row>
@@ -557,22 +557,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E3" t="n">
+        <v>21</v>
+      </c>
+      <c r="F3" t="n">
         <v>25</v>
       </c>
-      <c r="F3" t="n">
-        <v>35</v>
-      </c>
       <c r="G3" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
@@ -590,10 +590,10 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3491.5966</v>
+        <v>3489.329</v>
       </c>
       <c r="N3" t="n">
-        <v>94.93000000000001</v>
+        <v>94.98999999999999</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-05-24 05:27:59</t>
+          <t>2026-05-25 14:24:55</t>
         </is>
       </c>
     </row>
@@ -611,22 +611,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G4" t="n">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="H4" t="n">
         <v>2</v>
@@ -641,13 +641,13 @@
         <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>3486.942</v>
+        <v>3489.2238</v>
       </c>
       <c r="N4" t="n">
-        <v>94.88</v>
+        <v>94.98999999999999</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -656,7 +656,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-05-24 05:27:59</t>
+          <t>2026-05-25 14:24:55</t>
         </is>
       </c>
     </row>
@@ -665,22 +665,22 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E5" t="n">
         <v>25</v>
       </c>
       <c r="F5" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="G5" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H5" t="n">
         <v>2</v>
@@ -689,19 +689,19 @@
         <v>3</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3484.8948</v>
+        <v>3485.4473</v>
       </c>
       <c r="N5" t="n">
-        <v>94.86</v>
+        <v>94.95</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-05-24 05:27:59</t>
+          <t>2026-05-25 14:24:55</t>
         </is>
       </c>
     </row>
@@ -719,22 +719,22 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
         <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E6" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F6" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="G6" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="H6" t="n">
         <v>2</v>
@@ -749,13 +749,13 @@
         <v>2</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>3481.5906</v>
+        <v>3484.369</v>
       </c>
       <c r="N6" t="n">
-        <v>94.83</v>
+        <v>94.94</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-05-24 05:27:59</t>
+          <t>2026-05-25 14:24:55</t>
         </is>
       </c>
     </row>
@@ -773,22 +773,22 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E7" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F7" t="n">
         <v>27</v>
       </c>
       <c r="G7" t="n">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="H7" t="n">
         <v>2</v>
@@ -806,10 +806,10 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3481.191</v>
+        <v>3483.3709</v>
       </c>
       <c r="N7" t="n">
-        <v>94.83</v>
+        <v>94.93000000000001</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-05-24 05:27:59</t>
+          <t>2026-05-25 14:24:55</t>
         </is>
       </c>
     </row>
@@ -827,22 +827,22 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C8" t="n">
+        <v>8</v>
+      </c>
+      <c r="D8" t="n">
         <v>10</v>
-      </c>
-      <c r="D8" t="n">
-        <v>14</v>
       </c>
       <c r="E8" t="n">
         <v>25</v>
       </c>
       <c r="F8" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="G8" t="n">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="H8" t="n">
         <v>2</v>
@@ -857,13 +857,13 @@
         <v>2</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3479.293</v>
+        <v>3482.6956</v>
       </c>
       <c r="N8" t="n">
-        <v>94.81</v>
+        <v>94.92</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-05-24 05:27:59</t>
+          <t>2026-05-25 14:24:55</t>
         </is>
       </c>
     </row>
@@ -881,22 +881,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E9" t="n">
         <v>25</v>
       </c>
       <c r="F9" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G9" t="n">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="H9" t="n">
         <v>2</v>
@@ -911,13 +911,13 @@
         <v>2</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>3478.8735</v>
+        <v>3481.8143</v>
       </c>
       <c r="N9" t="n">
-        <v>94.8</v>
+        <v>94.91</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-05-24 05:27:59</t>
+          <t>2026-05-25 14:24:55</t>
         </is>
       </c>
     </row>
@@ -938,19 +938,19 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
         <v>25</v>
       </c>
       <c r="F10" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="G10" t="n">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="H10" t="n">
         <v>2</v>
@@ -968,10 +968,10 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3476.1629</v>
+        <v>3480.2732</v>
       </c>
       <c r="N10" t="n">
-        <v>94.78</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-05-24 05:27:59</t>
+          <t>2026-05-25 14:24:55</t>
         </is>
       </c>
     </row>
@@ -998,13 +998,13 @@
         <v>14</v>
       </c>
       <c r="E11" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F11" t="n">
         <v>25</v>
       </c>
       <c r="G11" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H11" t="n">
         <v>2</v>
@@ -1022,10 +1022,10 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3475.3186</v>
+        <v>3479.488</v>
       </c>
       <c r="N11" t="n">
-        <v>94.77</v>
+        <v>94.89</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-05-24 05:27:59</t>
+          <t>2026-05-25 14:24:55</t>
         </is>
       </c>
     </row>

--- a/data/exports/predictions/daily_lotto_predictions.xlsx
+++ b/data/exports/predictions/daily_lotto_predictions.xlsx
@@ -503,22 +503,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E2" t="n">
+        <v>21</v>
+      </c>
+      <c r="F2" t="n">
         <v>25</v>
       </c>
-      <c r="F2" t="n">
-        <v>33</v>
-      </c>
       <c r="G2" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H2" t="n">
         <v>2</v>
@@ -536,7 +536,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>3490.398</v>
+        <v>3492.39</v>
       </c>
       <c r="N2" t="n">
         <v>95</v>
@@ -548,7 +548,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-05-25 14:24:55</t>
+          <t>2026-05-26 14:15:42</t>
         </is>
       </c>
     </row>
@@ -557,13 +557,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3" t="n">
         <v>10</v>
       </c>
-      <c r="C3" t="n">
-        <v>12</v>
-      </c>
       <c r="D3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E3" t="n">
         <v>21</v>
@@ -572,7 +572,7 @@
         <v>25</v>
       </c>
       <c r="G3" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
@@ -590,10 +590,10 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3489.329</v>
+        <v>3488.2742</v>
       </c>
       <c r="N3" t="n">
-        <v>94.98999999999999</v>
+        <v>94.95999999999999</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-05-25 14:24:55</t>
+          <t>2026-05-26 14:15:42</t>
         </is>
       </c>
     </row>
@@ -611,22 +611,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F4" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="G4" t="n">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="H4" t="n">
         <v>2</v>
@@ -641,13 +641,13 @@
         <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3489.2238</v>
+        <v>3487.2754</v>
       </c>
       <c r="N4" t="n">
-        <v>94.98999999999999</v>
+        <v>94.95</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -656,7 +656,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-05-25 14:24:55</t>
+          <t>2026-05-26 14:15:42</t>
         </is>
       </c>
     </row>
@@ -665,13 +665,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
         <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
         <v>25</v>
@@ -680,7 +680,7 @@
         <v>27</v>
       </c>
       <c r="G5" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="H5" t="n">
         <v>2</v>
@@ -698,10 +698,10 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3485.4473</v>
+        <v>3486.7701</v>
       </c>
       <c r="N5" t="n">
-        <v>94.95</v>
+        <v>94.94</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-05-25 14:24:55</t>
+          <t>2026-05-26 14:15:42</t>
         </is>
       </c>
     </row>
@@ -719,22 +719,22 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C6" t="n">
         <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E6" t="n">
         <v>25</v>
       </c>
       <c r="F6" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G6" t="n">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="H6" t="n">
         <v>2</v>
@@ -743,19 +743,19 @@
         <v>3</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3484.369</v>
+        <v>3483.8445</v>
       </c>
       <c r="N6" t="n">
-        <v>94.94</v>
+        <v>94.91</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-05-25 14:24:55</t>
+          <t>2026-05-26 14:15:42</t>
         </is>
       </c>
     </row>
@@ -773,22 +773,22 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" t="n">
         <v>6</v>
       </c>
-      <c r="C7" t="n">
-        <v>10</v>
-      </c>
       <c r="D7" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F7" t="n">
         <v>27</v>
       </c>
       <c r="G7" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="H7" t="n">
         <v>2</v>
@@ -806,10 +806,10 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3483.3709</v>
+        <v>3483.3269</v>
       </c>
       <c r="N7" t="n">
-        <v>94.93000000000001</v>
+        <v>94.91</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-05-25 14:24:55</t>
+          <t>2026-05-26 14:15:42</t>
         </is>
       </c>
     </row>
@@ -827,22 +827,22 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E8" t="n">
+        <v>21</v>
+      </c>
+      <c r="F8" t="n">
         <v>25</v>
       </c>
-      <c r="F8" t="n">
-        <v>27</v>
-      </c>
       <c r="G8" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H8" t="n">
         <v>2</v>
@@ -851,19 +851,19 @@
         <v>3</v>
       </c>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3482.6956</v>
+        <v>3481.5484</v>
       </c>
       <c r="N8" t="n">
-        <v>94.92</v>
+        <v>94.89</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-05-25 14:24:55</t>
+          <t>2026-05-26 14:15:42</t>
         </is>
       </c>
     </row>
@@ -881,22 +881,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
         <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n">
         <v>25</v>
       </c>
       <c r="F9" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G9" t="n">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="H9" t="n">
         <v>2</v>
@@ -914,10 +914,10 @@
         <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>3481.8143</v>
+        <v>3481.4788</v>
       </c>
       <c r="N9" t="n">
-        <v>94.91</v>
+        <v>94.89</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-05-25 14:24:55</t>
+          <t>2026-05-26 14:15:42</t>
         </is>
       </c>
     </row>
@@ -935,22 +935,22 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E10" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F10" t="n">
         <v>27</v>
       </c>
       <c r="G10" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="H10" t="n">
         <v>2</v>
@@ -968,10 +968,10 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3480.2732</v>
+        <v>3480.6122</v>
       </c>
       <c r="N10" t="n">
-        <v>94.90000000000001</v>
+        <v>94.88</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-05-25 14:24:55</t>
+          <t>2026-05-26 14:15:42</t>
         </is>
       </c>
     </row>
@@ -989,22 +989,22 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F11" t="n">
         <v>25</v>
       </c>
       <c r="G11" t="n">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="H11" t="n">
         <v>2</v>
@@ -1013,19 +1013,19 @@
         <v>3</v>
       </c>
       <c r="J11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>3479.488</v>
+        <v>3479.0058</v>
       </c>
       <c r="N11" t="n">
-        <v>94.89</v>
+        <v>94.87</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-05-25 14:24:55</t>
+          <t>2026-05-26 14:15:42</t>
         </is>
       </c>
     </row>

--- a/data/exports/predictions/daily_lotto_predictions.xlsx
+++ b/data/exports/predictions/daily_lotto_predictions.xlsx
@@ -503,22 +503,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C2" t="n">
         <v>10</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>12</v>
       </c>
-      <c r="D2" t="n">
-        <v>15</v>
-      </c>
       <c r="E2" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F2" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G2" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H2" t="n">
         <v>2</v>
@@ -536,7 +536,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>3492.39</v>
+        <v>3515.6973</v>
       </c>
       <c r="N2" t="n">
         <v>95</v>
@@ -548,7 +548,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:42</t>
+          <t>2026-05-27 14:49:14</t>
         </is>
       </c>
     </row>
@@ -557,22 +557,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3" t="n">
         <v>10</v>
       </c>
       <c r="D3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E3" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F3" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="G3" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
@@ -590,10 +590,10 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3488.2742</v>
+        <v>3495.2584</v>
       </c>
       <c r="N3" t="n">
-        <v>94.95999999999999</v>
+        <v>94.8</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:42</t>
+          <t>2026-05-27 14:49:14</t>
         </is>
       </c>
     </row>
@@ -614,19 +614,19 @@
         <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
         <v>25</v>
       </c>
       <c r="F4" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="G4" t="n">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="H4" t="n">
         <v>2</v>
@@ -641,13 +641,13 @@
         <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M4" t="n">
-        <v>3487.2754</v>
+        <v>3493.2143</v>
       </c>
       <c r="N4" t="n">
-        <v>94.95</v>
+        <v>94.78</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -656,7 +656,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:42</t>
+          <t>2026-05-27 14:49:14</t>
         </is>
       </c>
     </row>
@@ -665,13 +665,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E5" t="n">
         <v>25</v>
@@ -680,7 +680,7 @@
         <v>27</v>
       </c>
       <c r="G5" t="n">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="H5" t="n">
         <v>2</v>
@@ -698,10 +698,10 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3486.7701</v>
+        <v>3491.6905</v>
       </c>
       <c r="N5" t="n">
-        <v>94.94</v>
+        <v>94.76000000000001</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:42</t>
+          <t>2026-05-27 14:49:14</t>
         </is>
       </c>
     </row>
@@ -719,22 +719,22 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6" t="n">
         <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F6" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="G6" t="n">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="H6" t="n">
         <v>2</v>
@@ -743,19 +743,19 @@
         <v>3</v>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3483.8445</v>
+        <v>3490.9613</v>
       </c>
       <c r="N6" t="n">
-        <v>94.91</v>
+        <v>94.75</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:42</t>
+          <t>2026-05-27 14:49:14</t>
         </is>
       </c>
     </row>
@@ -773,13 +773,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" t="n">
         <v>4</v>
       </c>
-      <c r="C7" t="n">
-        <v>6</v>
-      </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
         <v>25</v>
@@ -788,7 +788,7 @@
         <v>27</v>
       </c>
       <c r="G7" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H7" t="n">
         <v>2</v>
@@ -803,13 +803,13 @@
         <v>2</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>3483.3269</v>
+        <v>3489.8653</v>
       </c>
       <c r="N7" t="n">
-        <v>94.91</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:42</t>
+          <t>2026-05-27 14:49:14</t>
         </is>
       </c>
     </row>
@@ -830,19 +830,19 @@
         <v>4</v>
       </c>
       <c r="C8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" t="n">
         <v>10</v>
       </c>
-      <c r="D8" t="n">
-        <v>14</v>
-      </c>
       <c r="E8" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F8" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="G8" t="n">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H8" t="n">
         <v>2</v>
@@ -851,19 +851,19 @@
         <v>3</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3481.5484</v>
+        <v>3488.0971</v>
       </c>
       <c r="N8" t="n">
-        <v>94.89</v>
+        <v>94.73</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:42</t>
+          <t>2026-05-27 14:49:14</t>
         </is>
       </c>
     </row>
@@ -884,19 +884,19 @@
         <v>6</v>
       </c>
       <c r="C9" t="n">
+        <v>9</v>
+      </c>
+      <c r="D9" t="n">
         <v>10</v>
       </c>
-      <c r="D9" t="n">
-        <v>11</v>
-      </c>
       <c r="E9" t="n">
+        <v>21</v>
+      </c>
+      <c r="F9" t="n">
         <v>25</v>
       </c>
-      <c r="F9" t="n">
-        <v>33</v>
-      </c>
       <c r="G9" t="n">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="H9" t="n">
         <v>2</v>
@@ -914,10 +914,10 @@
         <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>3481.4788</v>
+        <v>3487.0875</v>
       </c>
       <c r="N9" t="n">
-        <v>94.89</v>
+        <v>94.72</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:42</t>
+          <t>2026-05-27 14:49:14</t>
         </is>
       </c>
     </row>
@@ -935,22 +935,22 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
         <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E10" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F10" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G10" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H10" t="n">
         <v>2</v>
@@ -965,13 +965,13 @@
         <v>2</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>3480.6122</v>
+        <v>3485.713</v>
       </c>
       <c r="N10" t="n">
-        <v>94.88</v>
+        <v>94.7</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:42</t>
+          <t>2026-05-27 14:49:14</t>
         </is>
       </c>
     </row>
@@ -989,22 +989,22 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E11" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F11" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="G11" t="n">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="H11" t="n">
         <v>2</v>
@@ -1013,19 +1013,19 @@
         <v>3</v>
       </c>
       <c r="J11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3479.0058</v>
+        <v>3483.6628</v>
       </c>
       <c r="N11" t="n">
-        <v>94.87</v>
+        <v>94.68000000000001</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:42</t>
+          <t>2026-05-27 14:49:14</t>
         </is>
       </c>
     </row>

--- a/data/exports/predictions/daily_lotto_predictions.xlsx
+++ b/data/exports/predictions/daily_lotto_predictions.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-05-27 14:49:14</t>
+          <t>2026-05-28 08:47:31</t>
         </is>
       </c>
     </row>
@@ -602,7 +602,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-05-27 14:49:14</t>
+          <t>2026-05-28 08:47:31</t>
         </is>
       </c>
     </row>
@@ -656,7 +656,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-05-27 14:49:14</t>
+          <t>2026-05-28 08:47:31</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-05-27 14:49:14</t>
+          <t>2026-05-28 08:47:31</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-05-27 14:49:14</t>
+          <t>2026-05-28 08:47:31</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-05-27 14:49:14</t>
+          <t>2026-05-28 08:47:31</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-05-27 14:49:14</t>
+          <t>2026-05-28 08:47:31</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-05-27 14:49:14</t>
+          <t>2026-05-28 08:47:31</t>
         </is>
       </c>
     </row>
@@ -980,7 +980,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-05-27 14:49:14</t>
+          <t>2026-05-28 08:47:31</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-05-27 14:49:14</t>
+          <t>2026-05-28 08:47:31</t>
         </is>
       </c>
     </row>

--- a/data/exports/predictions/daily_lotto_predictions.xlsx
+++ b/data/exports/predictions/daily_lotto_predictions.xlsx
@@ -506,10 +506,10 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E2" t="n">
         <v>25</v>
@@ -518,7 +518,7 @@
         <v>27</v>
       </c>
       <c r="G2" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="H2" t="n">
         <v>2</v>
@@ -536,7 +536,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>3515.6973</v>
+        <v>3513.4218</v>
       </c>
       <c r="N2" t="n">
         <v>95</v>
@@ -548,7 +548,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:31</t>
+          <t>2026-05-28 17:13:23</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
         <v>10</v>
@@ -569,10 +569,10 @@
         <v>25</v>
       </c>
       <c r="F3" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G3" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
@@ -590,10 +590,10 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3495.2584</v>
+        <v>3507.0603</v>
       </c>
       <c r="N3" t="n">
-        <v>94.8</v>
+        <v>94.94</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:31</t>
+          <t>2026-05-28 17:13:23</t>
         </is>
       </c>
     </row>
@@ -611,22 +611,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F4" t="n">
         <v>27</v>
       </c>
       <c r="G4" t="n">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="H4" t="n">
         <v>2</v>
@@ -641,13 +641,13 @@
         <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3493.2143</v>
+        <v>3492.893</v>
       </c>
       <c r="N4" t="n">
-        <v>94.78</v>
+        <v>94.8</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -656,7 +656,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:31</t>
+          <t>2026-05-28 17:13:23</t>
         </is>
       </c>
     </row>
@@ -665,19 +665,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D5" t="n">
         <v>10</v>
-      </c>
-      <c r="D5" t="n">
-        <v>13</v>
       </c>
       <c r="E5" t="n">
         <v>25</v>
       </c>
       <c r="F5" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="G5" t="n">
         <v>81</v>
@@ -698,10 +698,10 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3491.6905</v>
+        <v>3491.1013</v>
       </c>
       <c r="N5" t="n">
-        <v>94.76000000000001</v>
+        <v>94.78</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:31</t>
+          <t>2026-05-28 17:13:23</t>
         </is>
       </c>
     </row>
@@ -719,22 +719,22 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E6" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F6" t="n">
         <v>27</v>
       </c>
       <c r="G6" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H6" t="n">
         <v>2</v>
@@ -749,13 +749,13 @@
         <v>2</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>3490.9613</v>
+        <v>3490.2775</v>
       </c>
       <c r="N6" t="n">
-        <v>94.75</v>
+        <v>94.77</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:31</t>
+          <t>2026-05-28 17:13:23</t>
         </is>
       </c>
     </row>
@@ -773,22 +773,22 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
         <v>25</v>
       </c>
       <c r="F7" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="G7" t="n">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="H7" t="n">
         <v>2</v>
@@ -806,10 +806,10 @@
         <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>3489.8653</v>
+        <v>3490.2679</v>
       </c>
       <c r="N7" t="n">
-        <v>94.73999999999999</v>
+        <v>94.77</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:31</t>
+          <t>2026-05-28 17:13:23</t>
         </is>
       </c>
     </row>
@@ -827,19 +827,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E8" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F8" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="G8" t="n">
         <v>81</v>
@@ -860,10 +860,10 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3488.0971</v>
+        <v>3490.1666</v>
       </c>
       <c r="N8" t="n">
-        <v>94.73</v>
+        <v>94.77</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:31</t>
+          <t>2026-05-28 17:13:23</t>
         </is>
       </c>
     </row>
@@ -881,22 +881,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
         <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F9" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G9" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H9" t="n">
         <v>2</v>
@@ -911,13 +911,13 @@
         <v>2</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3487.0875</v>
+        <v>3489.6671</v>
       </c>
       <c r="N9" t="n">
-        <v>94.72</v>
+        <v>94.76000000000001</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:31</t>
+          <t>2026-05-28 17:13:23</t>
         </is>
       </c>
     </row>
@@ -935,22 +935,22 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
+        <v>6</v>
+      </c>
+      <c r="C10" t="n">
         <v>9</v>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>10</v>
       </c>
-      <c r="D10" t="n">
-        <v>14</v>
-      </c>
       <c r="E10" t="n">
+        <v>21</v>
+      </c>
+      <c r="F10" t="n">
         <v>25</v>
       </c>
-      <c r="F10" t="n">
-        <v>31</v>
-      </c>
       <c r="G10" t="n">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="H10" t="n">
         <v>2</v>
@@ -968,10 +968,10 @@
         <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>3485.713</v>
+        <v>3488.9524</v>
       </c>
       <c r="N10" t="n">
-        <v>94.7</v>
+        <v>94.76000000000001</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:31</t>
+          <t>2026-05-28 17:13:23</t>
         </is>
       </c>
     </row>
@@ -989,22 +989,22 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C11" t="n">
         <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E11" t="n">
+        <v>23</v>
+      </c>
+      <c r="F11" t="n">
         <v>25</v>
       </c>
-      <c r="F11" t="n">
-        <v>36</v>
-      </c>
       <c r="G11" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="H11" t="n">
         <v>2</v>
@@ -1013,19 +1013,19 @@
         <v>3</v>
       </c>
       <c r="J11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3483.6628</v>
+        <v>3488.0909</v>
       </c>
       <c r="N11" t="n">
-        <v>94.68000000000001</v>
+        <v>94.75</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:31</t>
+          <t>2026-05-28 17:13:23</t>
         </is>
       </c>
     </row>

--- a/data/exports/predictions/daily_lotto_predictions.xlsx
+++ b/data/exports/predictions/daily_lotto_predictions.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:23</t>
+          <t>2026-05-28 19:43:03</t>
         </is>
       </c>
     </row>
@@ -602,7 +602,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:23</t>
+          <t>2026-05-28 19:43:03</t>
         </is>
       </c>
     </row>
@@ -656,7 +656,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:23</t>
+          <t>2026-05-28 19:43:03</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:23</t>
+          <t>2026-05-28 19:43:03</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:23</t>
+          <t>2026-05-28 19:43:03</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:23</t>
+          <t>2026-05-28 19:43:03</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:23</t>
+          <t>2026-05-28 19:43:03</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:23</t>
+          <t>2026-05-28 19:43:03</t>
         </is>
       </c>
     </row>
@@ -980,7 +980,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:23</t>
+          <t>2026-05-28 19:43:03</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:23</t>
+          <t>2026-05-28 19:43:03</t>
         </is>
       </c>
     </row>
